--- a/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier. Maman dit : on va nommer un pays. William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue. Maman dit : ça, c'est un paysage. C'est la mer. William dit : la mer. Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
+          <t>William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier. On va nommer un pays. William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier.
+maman|On va nommer un pays.
+narrateur|William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue.
+maman|Ça, c'est un paysage. C'est la mer.
+enfant-m|La mer.
+narrateur|Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|William nomme l'Italie. Il nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|William a dit le nom. L'Italie. Il a dit le paysage. La mer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|William s'allonge près de maman. Il pense à l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|William nomme l'Italie. Il nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|William a dit le nom. L'Italie. Il a dit le paysage. La mer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|William s'allonge près de maman. Il pense à l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>William nomme un pays</t>
+          <t>Le livre de mer de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut voir la mer de France dans le livre cartonné. Une page colle. Elles tirent doucement. Le bleu s'ouvre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier. On va nommer un pays. William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
+          <t>Un rayon jaune chauffe le canapé bleu. Le coussin sent encore le savon. Une mouche tourne près de la vitre. Le salon est calme et chaud. Un livre cartonné attend par terre. Le livre est épais et lisse. Mila vit ici, avec maman. Tu as vu le livre, Mila ? Il est bleu, maman. Oui. C'est le livre de la mer. En ce moment, Mila s'assoit. Elle pose la main sur le livre. Je veux voir la mer. On ouvre ensemble ? Oui, maman. Mila tire une page. La page colle un peu. Elle colle ! On tire tout doucement ? Oui. Maman tient le bord. Mila tire encore un peu. Un bruit de papier se fait. Elle vient ! Encore un peu. La page se décolle, lentement. Un fil de colle reste brillant. Ça brille. C'est la colle. La page montre de l'eau bleue. La mer ! Oui, c'est la mer. Et le pays, tu vois ? Mila pose le doigt. C'est la France. La France. Et la mer. Un pays. Un paysage. Le carton est un peu chaud. Mila caresse le bleu. C'est mou ? Non. C'est du carton. Une petite tache de colle reste. Mila la touche du doigt. Ça colle encore. On laisse sécher ? Oui. Un bateau tout petit est dessiné. Un bateau ! Oui, sur la mer. La mer de France. Mila souffle sur la tache. Fffff. La colle devient moins brillante.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier. Maman dit : on va &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mer un pays. William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue. Maman dit : ça, c'est un paysage. C'est la mer. William dit : la mer. Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune chauffe le canapé bleu. Le coussin sent encore le savon. Une mouche tourne près de la vitre. Le salon est calme et chaud. Un livre cartonné attend par terre. Le livre est épais et lisse. Mila vit ici, avec maman. Tu as vu le livre, Mila ? Il est bleu, maman. Oui. C'est le livre de la mer. En ce moment, Mila s'assoit. Elle pose la main sur le livre. Je veux voir la mer. On ouvre ensemble ? Oui, maman. Mila tire une page. La page colle un peu. Elle colle ! On tire tout doucement ? Oui. Maman tient le bord. Mila tire encore un peu. Un bruit de papier se fait. Elle vient ! Encore un peu. La page se décolle, lentement. Un fil de colle reste brillant. Ça brille. C'est la colle. La page montre de l'eau bleue. La mer ! Oui, c'est la mer. Et le pays, tu vois ? Mila pose le doigt. C'est la France. La France. Et la mer. Un pays. Un paysage. Le carton est un peu chaud. Mila caresse le bleu. C'est mou ? Non. C'est du carton. Une petite tache de colle reste. Mila la touche du doigt. Ça colle encore. On laisse sécher ? Oui. Un bateau tout petit est dessiné. Un bateau ! Oui, sur la mer. La mer de France. Mila souffle sur la tache. Fffff. La colle devient moins brillante.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|William s'assoit près de maman. Maman ouvre un grand livre. Les pages sentent le papier.
-maman|On va nommer un pays.
-narrateur|William pose le doigt. Maman lit le nom : l'Italie. William répète : l'Italie. Sur la page, il y a de l'eau bleue.
-maman|Ça, c'est un paysage. C'est la mer.
-enfant-m|La mer.
-narrateur|Un pays. Un nom. Un paysage. L'Italie, et la mer. Maman ferme le livre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un rayon jaune chauffe le canapé bleu.
+narrateur|Le coussin sent encore le savon.
+narrateur|Une mouche tourne près de la vitre.
+narrateur|Le salon est calme et chaud.
+narrateur|Un livre cartonné attend par terre.
+narrateur|Le livre est épais et lisse.
+narrateur|Mila vit ici, avec maman.
+maman|Tu as vu le livre, Mila ?
+enfant-f|Il est bleu, maman.
+maman|Oui.
+maman|C'est le livre de la mer.
+narrateur|En ce moment, Mila s'assoit.
+narrateur|Elle pose la main sur le livre.
+enfant-f|Je veux voir la mer.
+maman|On ouvre ensemble ?
+enfant-f|Oui, maman.
+narrateur|Mila tire une page.
+narrateur|La page colle un peu.
+enfant-f|Elle colle !
+maman|On tire tout doucement ?
+enfant-f|Oui.
+narrateur|Maman tient le bord.
+narrateur|Mila tire encore un peu.
+narrateur|Un bruit de papier se fait.
+enfant-f|Elle vient !
+maman|Encore un peu.
+narrateur|La page se décolle, lentement.
+narrateur|Un fil de colle reste brillant.
+enfant-f|Ça brille.
+maman|C'est la colle.
+narrateur|La page montre de l'eau bleue.
+enfant-f|La mer !
+maman|Oui, c'est la mer.
+maman|Et le pays, tu vois ?
+narrateur|Mila pose le doigt.
+maman|C'est la France.
+enfant-f|La France.
+enfant-f|Et la mer.
+maman|Un pays.
+maman|Un paysage.
+narrateur|Le carton est un peu chaud.
+narrateur|Mila caresse le bleu.
+enfant-f|C'est mou ?
+maman|Non.
+maman|C'est du carton.
+narrateur|Une petite tache de colle reste.
+narrateur|Mila la touche du doigt.
+enfant-f|Ça colle encore.
+maman|On laisse sécher ?
+enfant-f|Oui.
+narrateur|Un bateau tout petit est dessiné.
+enfant-f|Un bateau !
+maman|Oui, sur la mer.
+maman|La mer de France.
+narrateur|Mila souffle sur la tache.
+enfant-f|Fffff.
+narrateur|La colle devient moins brillante.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1407,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>William nomme l'Italie. Il nomme aussi quoi ?</t>
+          <t>Mila nomme la France. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;William &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'Italie. Il nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila nomme la France. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1427,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la mer | un paysage | un pays | l'Italie</t>
+          <t>mer | la mer | eau | l'eau | mer de France</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1442,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a de l'eau bleue. C'est quel paysage ?</t>
+          <t>Mila nomme aussi la mer. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1491,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1567,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|William nomme l'Italie. Il nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila nomme la France.
+narrateur|Elle nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>William a dit le nom. L'Italie. Il a dit le paysage. La mer.</t>
+          <t>La mer. Oui, la mer. La page veut se refermer. Le carton ramène un peu. Elle se recolle ! On la tient ouverte. Mila pose la paume à plat. Maman tient l'autre bord. La mer reste toute bleue. Tu la vois bien ? Oui. Elle est grande. Merci, Mila. Le fil de colle sèche. Il ne brille plus. Le bateau est petit. Il glisse sur l'eau. Mila suit le bateau du doigt. Le carton fait un bruit mat.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;William a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. L'Italie. Il a dit le paysage. La mer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La mer. Oui, la mer. La page veut se refermer. Le carton ramène un peu. Elle se recolle ! On la tient ouverte. Mila pose la paume à plat. Maman tient l'autre bord. La mer reste toute bleue. Tu la vois bien ? Oui. Elle est grande. Merci, Mila. Le fil de colle sèche. Il ne brille plus. Le bateau est petit. Il glisse sur l'eau. Mila suit le bateau du doigt. Le carton fait un bruit mat.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1656,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1739,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|William a dit le nom. L'Italie. Il a dit le paysage. La mer.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|La mer.
+maman|Oui, la mer.
+narrateur|La page veut se refermer.
+narrateur|Le carton ramène un peu.
+enfant-f|Elle se recolle !
+maman|On la tient ouverte.
+narrateur|Mila pose la paume à plat.
+narrateur|Maman tient l'autre bord.
+narrateur|La mer reste toute bleue.
+maman|Tu la vois bien ?
+enfant-f|Oui.
+enfant-f|Elle est grande.
+maman|Merci, Mila.
+narrateur|Le fil de colle sèche.
+narrateur|Il ne brille plus.
+enfant-f|Le bateau est petit.
+maman|Il glisse sur l'eau.
+narrateur|Mila suit le bateau du doigt.
+narrateur|Le carton fait un bruit mat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>William s'allonge près de maman. Il pense à l'eau.</t>
+          <t>On ferme tout doucement ? Encore un peu. Elles regardent le bleu encore. La mouche a quitté la vitre. Tu as fini de regarder ? Oui, maman. Mila referme le livre. La page ne colle plus. La France. La mer. Oui. Le livre reste sur le canapé. Le rayon jaune le touche encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;William s'allonge près de maman. Il pense à l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On ferme tout doucement ? Encore un peu. Elles regardent le bleu encore. La mouche a quitté la vitre. Tu as fini de regarder ? Oui, maman. Mila referme le livre. La page ne colle plus. La France. La mer. Oui. Le livre reste sur le canapé. Le rayon jaune le touche encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,14 +1845,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1920,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|William s'allonge près de maman. Il pense à l'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|On ferme tout doucement ?
+enfant-f|Encore un peu.
+narrateur|Elles regardent le bleu encore.
+narrateur|La mouche a quitté la vitre.
+maman|Tu as fini de regarder ?
+enfant-f|Oui, maman.
+narrateur|Mila referme le livre.
+narrateur|La page ne colle plus.
+enfant-f|La France.
+enfant-f|La mer.
+maman|Oui.
+narrateur|Le livre reste sur le canapé.
+narrateur|Le rayon jaune le touche encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le carton sent encore la colle. Un coin bleu dépasse un peu. La mer est dedans. Elle t'attend. Le canapé garde le livre au chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le carton sent encore la colle. Un coin bleu dépasse un peu. La mer est dedans. Elle t'attend. Le canapé garde le livre au chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,14 +2020,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2099,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le carton sent encore la colle.
+narrateur|Un coin bleu dépasse un peu.
+enfant-f|La mer est dedans.
+maman|Elle t'attend.
+narrateur|Le canapé garde le livre au chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, canapé au soleil</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>William, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
